--- a/Datas/Role.xlsx
+++ b/Datas/Role.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="21045" windowHeight="8220"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -121,7 +121,7 @@
     <t>小蓝人的背景故事</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Role_Blue</t>
+    <t>Arts/UI/Prepare/Role_Mail</t>
   </si>
   <si>
     <t>示例</t>
@@ -148,7 +148,7 @@
     <t>小红人的背景故事</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Role_Red</t>
+    <t>Arts/UI/Prepare/Role_Femail</t>
   </si>
   <si>
     <t>ZiWei</t>
@@ -1265,7 +1265,9 @@
     <col min="4" max="7" width="14.625" customWidth="1"/>
     <col min="8" max="9" width="28.625" customWidth="1"/>
     <col min="10" max="10" width="56.625" customWidth="1"/>
-    <col min="11" max="14" width="28.625" customWidth="1"/>
+    <col min="11" max="12" width="28.625" customWidth="1"/>
+    <col min="13" max="13" width="36.5" customWidth="1"/>
+    <col min="14" max="14" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:14">

--- a/Datas/Role.xlsx
+++ b/Datas/Role.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21045" windowHeight="8220"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -121,7 +121,7 @@
     <t>小蓝人的背景故事</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Role_Mail</t>
+    <t>Arts/UI/Prepare/JS_A_boy_0001</t>
   </si>
   <si>
     <t>示例</t>
@@ -148,7 +148,7 @@
     <t>小红人的背景故事</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Role_Femail</t>
+    <t>Arts/UI/Prepare/JS_B_gril_0001</t>
   </si>
   <si>
     <t>ZiWei</t>
@@ -169,7 +169,7 @@
     <t>紫薇的背景故事</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Role_ZiWei</t>
+    <t>Arts/UI/Prepare/JS_C_ziwei_0001</t>
   </si>
   <si>
     <t>DaMeiLi</t>
@@ -190,7 +190,7 @@
     <t>大美丽的背景故事</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Role_DaMeiLi</t>
+    <t>Arts/UI/Prepare/JS_D_dameiri_0001</t>
   </si>
   <si>
     <t>JinZhuangYuan</t>
@@ -211,7 +211,7 @@
     <t>金状元的背景故事</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Role_JinZhuangYuan</t>
+    <t>Arts/UI/Prepare/JS_E_jinzhuangyuan_0001</t>
   </si>
   <si>
     <t>YaKeDong</t>
@@ -232,7 +232,7 @@
     <t>亚克东的背景故事</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/Role_YaKeDong</t>
+    <t>Arts/UI/Prepare/JS_F_yakedong_0001</t>
   </si>
 </sst>
 </file>

--- a/Datas/Role.xlsx
+++ b/Datas/Role.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -121,7 +121,7 @@
     <t>小蓝人的背景故事</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/JS_A_boy_0001</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Roles/JS_A_boy_0001</t>
   </si>
   <si>
     <t>示例</t>
@@ -148,7 +148,7 @@
     <t>小红人的背景故事</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/JS_B_gril_0001</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Roles/JS_B_gril_0001</t>
   </si>
   <si>
     <t>ZiWei</t>
@@ -169,7 +169,7 @@
     <t>紫薇的背景故事</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/JS_C_ziwei_0001</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Roles/JS_C_ziwei_0001</t>
   </si>
   <si>
     <t>DaMeiLi</t>
@@ -190,7 +190,7 @@
     <t>大美丽的背景故事</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/JS_D_dameiri_0001</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Roles/JS_D_dameiri_0001</t>
   </si>
   <si>
     <t>JinZhuangYuan</t>
@@ -211,7 +211,7 @@
     <t>金状元的背景故事</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/JS_E_jinzhuangyuan_0001</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Roles/JS_E_jinzhuangyuan_0001</t>
   </si>
   <si>
     <t>YaKeDong</t>
@@ -232,7 +232,7 @@
     <t>亚克东的背景故事</t>
   </si>
   <si>
-    <t>Arts/UI/Prepare/JS_F_yakedong_0001</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Roles/JS_F_yakedong_0001</t>
   </si>
 </sst>
 </file>
@@ -932,19 +932,19 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1266,7 +1266,7 @@
     <col min="8" max="9" width="28.625" customWidth="1"/>
     <col min="10" max="10" width="56.625" customWidth="1"/>
     <col min="11" max="12" width="28.625" customWidth="1"/>
-    <col min="13" max="13" width="36.5" customWidth="1"/>
+    <col min="13" max="13" width="56.625" customWidth="1"/>
     <col min="14" max="14" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1288,7 +1288,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
-      <c r="J1" s="4"/>
+      <c r="J1" s="7"/>
       <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1312,15 +1312,15 @@
       <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="7"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="8"/>
       <c r="K2" s="1" t="s">
         <v>9</v>
       </c>
@@ -1344,15 +1344,15 @@
       <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="7"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="8"/>
       <c r="K3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,15 +1376,15 @@
       <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="7"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="8"/>
       <c r="K4" s="1" t="s">
         <v>19</v>
       </c>
@@ -1399,259 +1399,259 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:14">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6">
         <v>1</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="6">
         <v>170</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="6">
         <v>1</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="6">
         <v>-1</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="M5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="N5" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:14">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6">
         <v>2</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="6">
         <v>170</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="6">
         <v>1</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="6">
         <v>-1</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:14">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6">
         <v>3</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="6">
         <v>170</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="6">
         <v>2</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="6">
         <v>1</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="N7" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:14">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6">
         <v>4</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="6">
         <v>170</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="6">
         <v>3</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="6">
         <v>2</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="M8" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="N8" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:14">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6">
         <v>5</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="6">
         <v>170</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="6">
         <v>4</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="6">
         <v>3</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="N9" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:14">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6">
         <v>6</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="6">
         <v>170</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="6">
         <v>5</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="6">
         <v>4</v>
       </c>
-      <c r="M10" s="8" t="s">
+      <c r="M10" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="N10" s="8" t="s">
+      <c r="N10" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" ht="17.25" spans="1:14">
-      <c r="N11" s="8"/>
+    <row r="11" ht="17.25" spans="14:14">
+      <c r="N11" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Datas/Role.xlsx
+++ b/Datas/Role.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="76">
   <si>
     <t>##var</t>
   </si>
@@ -49,7 +49,10 @@
     <t>LinkedMapId</t>
   </si>
   <si>
-    <t>RoleImageResourcePath</t>
+    <t>IconResourcePath</t>
+  </si>
+  <si>
+    <t>VideoResourcePath</t>
   </si>
   <si>
     <t>Comment</t>
@@ -94,7 +97,10 @@
     <t>关联地图ID</t>
   </si>
   <si>
-    <t>角色图片资源路径</t>
+    <t>图标资源路径</t>
+  </si>
+  <si>
+    <t>视频资源路径</t>
   </si>
   <si>
     <t>注释</t>
@@ -124,6 +130,9 @@
     <t>Assets/Arts/UI/Sprites/Prepare/Roles/JS_A_boy_0001</t>
   </si>
   <si>
+    <t>Blue.mp4</t>
+  </si>
+  <si>
     <t>示例</t>
   </si>
   <si>
@@ -151,6 +160,9 @@
     <t>Assets/Arts/UI/Sprites/Prepare/Roles/JS_B_gril_0001</t>
   </si>
   <si>
+    <t>Red.mp4</t>
+  </si>
+  <si>
     <t>ZiWei</t>
   </si>
   <si>
@@ -172,6 +184,9 @@
     <t>Assets/Arts/UI/Sprites/Prepare/Roles/JS_C_ziwei_0001</t>
   </si>
   <si>
+    <t>ZiWei.mp4</t>
+  </si>
+  <si>
     <t>DaMeiLi</t>
   </si>
   <si>
@@ -193,6 +208,9 @@
     <t>Assets/Arts/UI/Sprites/Prepare/Roles/JS_D_dameiri_0001</t>
   </si>
   <si>
+    <t>DaMeiLi.mp4</t>
+  </si>
+  <si>
     <t>JinZhuangYuan</t>
   </si>
   <si>
@@ -214,6 +232,9 @@
     <t>Assets/Arts/UI/Sprites/Prepare/Roles/JS_E_jinzhuangyuan_0001</t>
   </si>
   <si>
+    <t>JinZhuangYuan.mp4</t>
+  </si>
+  <si>
     <t>YaKeDong</t>
   </si>
   <si>
@@ -233,6 +254,9 @@
   </si>
   <si>
     <t>Assets/Arts/UI/Sprites/Prepare/Roles/JS_F_yakedong_0001</t>
+  </si>
+  <si>
+    <t>YaKeDong.mp4</t>
   </si>
 </sst>
 </file>
@@ -1258,19 +1282,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="3" width="28.625" customWidth="1"/>
+    <col min="1" max="2" width="28.625" customWidth="1"/>
+    <col min="3" max="3" width="48.625" customWidth="1"/>
     <col min="4" max="7" width="14.625" customWidth="1"/>
     <col min="8" max="9" width="28.625" customWidth="1"/>
     <col min="10" max="10" width="56.625" customWidth="1"/>
     <col min="11" max="12" width="28.625" customWidth="1"/>
-    <col min="13" max="13" width="56.625" customWidth="1"/>
-    <col min="14" max="14" width="28.625" customWidth="1"/>
+    <col min="13" max="13" width="76.625" customWidth="1"/>
+    <col min="14" max="15" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:14">
+    <row r="1" ht="28" customHeight="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1301,19 +1326,22 @@
       <c r="N1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:14">
+    <row r="2" ht="28" customHeight="1" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -1322,30 +1350,33 @@
       <c r="I2" s="5"/>
       <c r="J2" s="8"/>
       <c r="K2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:14">
+    <row r="3" ht="28" customHeight="1" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
@@ -1354,30 +1385,33 @@
       <c r="I3" s="5"/>
       <c r="J3" s="8"/>
       <c r="K3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:14">
+    <row r="4" ht="28" customHeight="1" spans="1:15">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -1386,46 +1420,49 @@
       <c r="I4" s="5"/>
       <c r="J4" s="8"/>
       <c r="K4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1" spans="1:14">
+    <row r="5" ht="28" customHeight="1" spans="1:15">
       <c r="A5" s="6"/>
       <c r="B5" s="6">
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F5" s="6">
         <v>170</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K5" s="6">
         <v>1</v>
@@ -1434,40 +1471,43 @@
         <v>-1</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:14">
+    <row r="6" ht="28" customHeight="1" spans="1:15">
       <c r="A6" s="6"/>
       <c r="B6" s="6">
         <v>2</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F6" s="6">
         <v>170</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K6" s="6">
         <v>1</v>
@@ -1476,40 +1516,43 @@
         <v>-1</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>31</v>
+        <v>43</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:14">
+    <row r="7" ht="28" customHeight="1" spans="1:15">
       <c r="A7" s="6"/>
       <c r="B7" s="6">
         <v>3</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F7" s="6">
         <v>170</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K7" s="6">
         <v>2</v>
@@ -1518,40 +1561,43 @@
         <v>1</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>31</v>
+        <v>51</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1" spans="1:14">
+    <row r="8" ht="28" customHeight="1" spans="1:15">
       <c r="A8" s="6"/>
       <c r="B8" s="6">
         <v>4</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F8" s="6">
         <v>170</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K8" s="6">
         <v>3</v>
@@ -1560,40 +1606,43 @@
         <v>2</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>31</v>
+        <v>59</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1" spans="1:14">
+    <row r="9" ht="28" customHeight="1" spans="1:15">
       <c r="A9" s="6"/>
       <c r="B9" s="6">
         <v>5</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F9" s="6">
         <v>170</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K9" s="6">
         <v>4</v>
@@ -1602,40 +1651,43 @@
         <v>3</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>31</v>
+        <v>67</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1" spans="1:14">
+    <row r="10" ht="28" customHeight="1" spans="1:15">
       <c r="A10" s="6"/>
       <c r="B10" s="6">
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F10" s="6">
         <v>170</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="K10" s="6">
         <v>5</v>
@@ -1644,14 +1696,18 @@
         <v>4</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>31</v>
+        <v>75</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="11" ht="17.25" spans="14:14">
+    <row r="11" ht="17.25" spans="14:15">
       <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Datas/Role.xlsx
+++ b/Datas/Role.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -127,7 +127,7 @@
     <t>小蓝人的背景故事</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Prepare/Roles/JS_A_boy_0001</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Main/Roles/JS_A_boy_0001</t>
   </si>
   <si>
     <t>Blue.mp4</t>
@@ -157,7 +157,7 @@
     <t>小红人的背景故事</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Prepare/Roles/JS_B_gril_0001</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Main/Roles/JS_B_gril_0001</t>
   </si>
   <si>
     <t>Red.mp4</t>
@@ -181,7 +181,7 @@
     <t>紫薇的背景故事</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Prepare/Roles/JS_C_ziwei_0001</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Main/Roles/JS_C_ziwei_0001</t>
   </si>
   <si>
     <t>ZiWei.mp4</t>
@@ -205,7 +205,7 @@
     <t>大美丽的背景故事</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Prepare/Roles/JS_D_dameiri_0001</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Main/Roles/JS_D_dameiri_0001</t>
   </si>
   <si>
     <t>DaMeiLi.mp4</t>
@@ -229,7 +229,7 @@
     <t>金状元的背景故事</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Prepare/Roles/JS_E_jinzhuangyuan_0001</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Main/Roles/JS_E_jinzhuangyuan_0001</t>
   </si>
   <si>
     <t>JinZhuangYuan.mp4</t>
@@ -253,7 +253,7 @@
     <t>亚克东的背景故事</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Prepare/Roles/JS_F_yakedong_0001</t>
+    <t>Assets/Arts/UI/Sprites/Prepare/Main/Roles/JS_F_yakedong_0001</t>
   </si>
   <si>
     <t>YaKeDong.mp4</t>
@@ -956,19 +956,19 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1313,7 +1313,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
-      <c r="J1" s="7"/>
+      <c r="J1" s="4"/>
       <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1340,15 +1340,15 @@
       <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="8"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="7"/>
       <c r="K2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1375,15 +1375,15 @@
       <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="8"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="7"/>
       <c r="K3" s="1" t="s">
         <v>15</v>
       </c>
@@ -1410,15 +1410,15 @@
       <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="8"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="7"/>
       <c r="K4" s="1" t="s">
         <v>20</v>
       </c>
@@ -1436,278 +1436,278 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:15">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="8">
         <v>170</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="8">
         <v>1</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="8">
         <v>-1</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="8" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:15">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8">
         <v>2</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="8">
         <v>170</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="8">
         <v>1</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="8">
         <v>-1</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="6" t="s">
+      <c r="O6" s="8" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:15">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8">
         <v>3</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="8">
         <v>170</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="8">
         <v>2</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="8">
         <v>1</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="N7" s="6" t="s">
+      <c r="N7" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="O7" s="8" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:15">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="8">
         <v>170</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="8">
         <v>3</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="8">
         <v>2</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="N8" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="O8" s="8" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:15">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8">
         <v>5</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="8">
         <v>170</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="8">
         <v>4</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="8">
         <v>3</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="N9" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="O9" s="6" t="s">
+      <c r="O9" s="8" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:15">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8">
         <v>6</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="8">
         <v>170</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="8">
         <v>5</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="8">
         <v>4</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="N10" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="O10" s="6" t="s">
+      <c r="O10" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" ht="17.25" spans="14:15">
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
+    <row r="11" ht="17.25" spans="1:15">
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Datas/Role.xlsx
+++ b/Datas/Role.xlsx
@@ -109,7 +109,7 @@
     <t>Bule</t>
   </si>
   <si>
-    <t>小蓝人</t>
+    <t>小蓝仔</t>
   </si>
   <si>
     <t>小蓝星</t>
@@ -139,7 +139,7 @@
     <t>Red</t>
   </si>
   <si>
-    <t>小红人</t>
+    <t>小粉妹</t>
   </si>
   <si>
     <t>小红星</t>
@@ -166,7 +166,7 @@
     <t>ZiWei</t>
   </si>
   <si>
-    <t>紫薇</t>
+    <t>格格</t>
   </si>
   <si>
     <t>紫薇家乡</t>
@@ -178,7 +178,7 @@
     <t>紫薇的个性描述</t>
   </si>
   <si>
-    <t>紫薇的背景故事</t>
+    <t>格格的背景故事</t>
   </si>
   <si>
     <t>Assets/Arts/UI/Sprites/Prepare/Main/Roles/JS_C_ziwei_0001</t>

--- a/Datas/Role.xlsx
+++ b/Datas/Role.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -46,18 +46,9 @@
     <t>LinkedSkillId</t>
   </si>
   <si>
-    <t>LinkedMapId</t>
-  </si>
-  <si>
     <t>IconResourcePath</t>
   </si>
   <si>
-    <t>VideoResourcePath</t>
-  </si>
-  <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -94,169 +85,79 @@
     <t>关联技能ID</t>
   </si>
   <si>
-    <t>关联地图ID</t>
-  </si>
-  <si>
     <t>图标资源路径</t>
   </si>
   <si>
-    <t>视频资源路径</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
     <t>Bule</t>
   </si>
   <si>
     <t>小蓝仔</t>
   </si>
   <si>
-    <t>小蓝星</t>
-  </si>
-  <si>
-    <t>男</t>
-  </si>
-  <si>
-    <t>小蓝人的特征描述</t>
-  </si>
-  <si>
-    <t>小蓝人的个性描述</t>
-  </si>
-  <si>
-    <t>小蓝人的背景故事</t>
+    <t>小蓝仔是个爱穿蓝衣服的普通男孩，每天帮妈妈浇花、帮爸爸拿报纸。他不太会说话，但心地特别好。谁有困难，他都会悄悄出现，像一阵蓝色的风，轻轻帮完忙就笑着跑开啦。</t>
   </si>
   <si>
     <t>Assets/Arts/UI/Sprites/Prepare/Main/Roles/JS_A_boy_0001</t>
   </si>
   <si>
-    <t>Blue.mp4</t>
-  </si>
-  <si>
-    <t>示例</t>
-  </si>
-  <si>
     <t>Red</t>
   </si>
   <si>
     <t>小粉妹</t>
   </si>
   <si>
-    <t>小红星</t>
-  </si>
-  <si>
-    <t>女</t>
-  </si>
-  <si>
-    <t>小红人的特征描述</t>
-  </si>
-  <si>
-    <t>小红人的个性描述</t>
-  </si>
-  <si>
-    <t>小红人的背景故事</t>
+    <t>小粉妹是个穿粉裙子的小姑娘，喜欢唱歌和分糖果。她记不住路，却记得每个朋友爱吃什么。每天蹦蹦跳跳，像颗粉色的糖豆。她说：“甜甜地过日子，比什么都重要呀！”</t>
   </si>
   <si>
     <t>Assets/Arts/UI/Sprites/Prepare/Main/Roles/JS_B_gril_0001</t>
   </si>
   <si>
-    <t>Red.mp4</t>
-  </si>
-  <si>
     <t>ZiWei</t>
   </si>
   <si>
     <t>格格</t>
   </si>
   <si>
-    <t>紫薇家乡</t>
-  </si>
-  <si>
-    <t>紫薇的特征描述</t>
-  </si>
-  <si>
-    <t>紫薇的个性描述</t>
-  </si>
-  <si>
-    <t>格格的背景故事</t>
+    <t>格格是个聪明又温柔的小姑娘，住在小胡同里。她会背诗，会绣花，还会帮邻居奶奶读信。她眼睛里有星星，笑起来像春天的风。</t>
   </si>
   <si>
     <t>Assets/Arts/UI/Sprites/Prepare/Main/Roles/JS_C_ziwei_0001</t>
   </si>
   <si>
-    <t>ZiWei.mp4</t>
-  </si>
-  <si>
     <t>DaMeiLi</t>
   </si>
   <si>
     <t>大美丽</t>
   </si>
   <si>
-    <t>大美丽家乡</t>
-  </si>
-  <si>
-    <t>大美丽的特征描述</t>
-  </si>
-  <si>
-    <t>大美丽的个性描述</t>
-  </si>
-  <si>
-    <t>大美丽的背景故事</t>
+    <t>大美丽最爱美啦！每天出门前，要照十八遍镜子，裙子要转三圈才满意。她常说：“漂亮不是给别人看的，是让自己开心的！”她还会帮小朋友扎蝴蝶结，大家都喜欢她。</t>
   </si>
   <si>
     <t>Assets/Arts/UI/Sprites/Prepare/Main/Roles/JS_D_dameiri_0001</t>
   </si>
   <si>
-    <t>DaMeiLi.mp4</t>
-  </si>
-  <si>
     <t>JinZhuangYuan</t>
   </si>
   <si>
     <t>金状元</t>
   </si>
   <si>
-    <t>金状元家乡</t>
-  </si>
-  <si>
-    <t>金状元的特征描述</t>
-  </si>
-  <si>
-    <t>金状元的个性描述</t>
-  </si>
-  <si>
-    <t>金状元的背景故事</t>
+    <t>金状元是个爱直播的热心大哥，天天举着手机喊：“老铁们，今天又学会一道菜！”他有点油嘴滑舌，但心肠热。谁家吵架她都去劝，直播间里笑声不断。</t>
   </si>
   <si>
     <t>Assets/Arts/UI/Sprites/Prepare/Main/Roles/JS_E_jinzhuangyuan_0001</t>
   </si>
   <si>
-    <t>JinZhuangYuan.mp4</t>
-  </si>
-  <si>
     <t>YaKeDong</t>
   </si>
   <si>
     <t>亚克东</t>
   </si>
   <si>
-    <t>亚克东家乡</t>
-  </si>
-  <si>
-    <t>亚克东的特征描述</t>
-  </si>
-  <si>
-    <t>亚克东的个性描述</t>
-  </si>
-  <si>
-    <t>亚克东的背景故事</t>
+    <t>亚克东是个卖烤羊肉串的老头，一边烤一边念叨：“今天肯定发财！”他有点贪财，还有点迷信，但最疼小孙女。每次收摊，都给她留一串最大的肉，笑呵呵地说：“爷爷的宝贝，比钱重要！”</t>
   </si>
   <si>
     <t>Assets/Arts/UI/Sprites/Prepare/Main/Roles/JS_F_yakedong_0001</t>
-  </si>
-  <si>
-    <t>YaKeDong.mp4</t>
   </si>
 </sst>
 </file>
@@ -635,7 +536,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -662,17 +563,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin">
         <color auto="1"/>
@@ -819,7 +709,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -831,34 +721,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
@@ -943,7 +833,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -956,16 +846,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1282,20 +1166,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="28.625" customWidth="1"/>
     <col min="3" max="3" width="48.625" customWidth="1"/>
-    <col min="4" max="7" width="14.625" customWidth="1"/>
-    <col min="8" max="9" width="28.625" customWidth="1"/>
-    <col min="10" max="10" width="56.625" customWidth="1"/>
-    <col min="11" max="12" width="28.625" customWidth="1"/>
-    <col min="13" max="13" width="76.625" customWidth="1"/>
-    <col min="14" max="15" width="28.625" customWidth="1"/>
+    <col min="4" max="4" width="14.625" customWidth="1"/>
+    <col min="5" max="5" width="56.625" customWidth="1"/>
+    <col min="6" max="6" width="28.625" customWidth="1"/>
+    <col min="7" max="7" width="76.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:15">
+    <row r="1" ht="28" customHeight="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1309,412 +1191,208 @@
         <v>3</v>
       </c>
       <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="D2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:15">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:7">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:7">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>13</v>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:15">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>15</v>
+    <row r="5" ht="28" customHeight="1" spans="1:7">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:15">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N4" s="1" t="s">
+    <row r="6" ht="28" customHeight="1" spans="1:7">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6">
+        <v>2</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="D6" s="6" t="s">
         <v>24</v>
       </c>
+      <c r="E6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="6">
+        <v>1</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="5" ht="28" customHeight="1" spans="1:15">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8">
-        <v>1</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="8" t="s">
+    <row r="7" ht="28" customHeight="1" spans="1:7">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6">
+        <v>3</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="8">
-        <v>170</v>
-      </c>
-      <c r="G5" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="E7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="F7" s="6">
+        <v>2</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="8" t="s">
+    </row>
+    <row r="8" ht="28" customHeight="1" spans="1:7">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6">
+        <v>4</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="8">
-        <v>1</v>
-      </c>
-      <c r="L5" s="8">
-        <v>-1</v>
-      </c>
-      <c r="M5" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="E8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="F8" s="6">
+        <v>3</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:15">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8">
-        <v>2</v>
-      </c>
-      <c r="C6" s="8" t="s">
+    <row r="9" ht="28" customHeight="1" spans="1:7">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6">
+        <v>5</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="8">
-        <v>170</v>
-      </c>
-      <c r="G6" s="8" t="s">
+      <c r="F9" s="6">
+        <v>4</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="8" t="s">
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:7">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6">
+        <v>6</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="D10" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="E10" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K6" s="8">
-        <v>1</v>
-      </c>
-      <c r="L6" s="8">
-        <v>-1</v>
-      </c>
-      <c r="M6" s="8" t="s">
+      <c r="F10" s="6">
+        <v>5</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="N6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:15">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8">
-        <v>3</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="8">
-        <v>170</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K7" s="8">
-        <v>2</v>
-      </c>
-      <c r="L7" s="8">
-        <v>1</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:15">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8">
-        <v>4</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="8">
-        <v>170</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="K8" s="8">
-        <v>3</v>
-      </c>
-      <c r="L8" s="8">
-        <v>2</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:15">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8">
-        <v>5</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F9" s="8">
-        <v>170</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="K9" s="8">
-        <v>4</v>
-      </c>
-      <c r="L9" s="8">
-        <v>3</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="O9" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:15">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8">
-        <v>6</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="8">
-        <v>170</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="K10" s="8">
-        <v>5</v>
-      </c>
-      <c r="L10" s="8">
-        <v>4</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="N10" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" ht="17.25" spans="1:15">
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="D1:J1"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D3:J3"/>
-    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
